--- a/test-files/adjacency-matrix-modifications/special-characters-within-matrix/0-b-within-matrix-input.xlsx
+++ b/test-files/adjacency-matrix-modifications/special-characters-within-matrix/0-b-within-matrix-input.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="25915"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10222"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maikatran/GRNsight/beta/GRNsight/test-files/adjacency-matrix-modifications/special-characters-within-matrix/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A76D98-9A76-1240-99F2-6E9943D54CC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14240" firstSheet="7" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14240" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +26,7 @@
     <sheet name="network_optimized_b" sheetId="11" r:id="rId11"/>
     <sheet name="concentration_sigmas" sheetId="13" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="125725" concurrentCalc="0"/>
+  <calcPr calcId="125725"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -30,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="51">
   <si>
     <t>SystematicName</t>
   </si>
@@ -181,11 +187,14 @@
   <si>
     <t>0b</t>
   </si>
+  <si>
+    <t>cols regulators/rows targets</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -248,6 +257,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -572,9 +589,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -586,11 +603,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:V22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>47</v>
       </c>
@@ -658,7 +675,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -726,7 +743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -794,7 +811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -862,7 +879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -930,7 +947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -998,7 +1015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1066,7 +1083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1134,7 +1151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1202,7 +1219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1270,7 +1287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -1338,7 +1355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1406,7 +1423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1474,7 +1491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -1542,7 +1559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1610,7 +1627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -1678,7 +1695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1746,7 +1763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -1814,7 +1831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -1882,7 +1899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -1950,7 +1967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -2018,7 +2035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -2097,11 +2114,11 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2112,7 +2129,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2123,7 +2140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2134,7 +2151,7 @@
         <v>0.65031415394516434</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2145,7 +2162,7 @@
         <v>1.1608735890637201</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2156,7 +2173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2167,7 +2184,7 @@
         <v>4.723434337016859</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2178,7 +2195,7 @@
         <v>2.2093965892822576</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -2189,7 +2206,7 @@
         <v>1.4838022384341765</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -2200,7 +2217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2211,7 +2228,7 @@
         <v>4.3880758825533226</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -2222,7 +2239,7 @@
         <v>1.4292526942022845</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -2233,7 +2250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2244,7 +2261,7 @@
         <v>0.21204144369617425</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2255,7 +2272,7 @@
         <v>3.1826495298927981</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -2266,7 +2283,7 @@
         <v>0.83154851292891641</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2277,7 +2294,7 @@
         <v>5.312232618008994</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -2288,7 +2305,7 @@
         <v>0.30350389708240194</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -2299,7 +2316,7 @@
         <v>1.090960278752473</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -2310,7 +2327,7 @@
         <v>2.9644811435403602</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -2321,7 +2338,7 @@
         <v>1.411956405672939</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -2332,7 +2349,7 @@
         <v>1.0908187404229068</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -2354,11 +2371,11 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2375,7 +2392,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2392,7 +2409,7 @@
         <v>0.69315515241602899</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2409,7 +2426,7 @@
         <v>0.92245951116837099</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2426,7 +2443,7 @@
         <v>0.320493749001932</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2443,7 +2460,7 @@
         <v>0.70281582595053704</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2460,7 +2477,7 @@
         <v>0.80891828959740097</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2477,7 +2494,7 @@
         <v>0.78157727034137603</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -2494,7 +2511,7 @@
         <v>0.60748498565234699</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -2511,7 +2528,7 @@
         <v>0.54723644512184799</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2528,7 +2545,7 @@
         <v>1.09985790153451</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -2545,7 +2562,7 @@
         <v>0.65825511050072905</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -2562,7 +2579,7 @@
         <v>0.248881921070051</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2579,7 +2596,7 @@
         <v>1.2436321609087699</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2596,7 +2613,7 @@
         <v>0.76246682595887705</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -2613,7 +2630,7 @@
         <v>0.389622153973187</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2630,7 +2647,7 @@
         <v>0.44772738659776701</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -2647,7 +2664,7 @@
         <v>1.07122097617887</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -2664,7 +2681,7 @@
         <v>0.35000209622478101</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -2681,7 +2698,7 @@
         <v>0.89902628670097295</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -2698,7 +2715,7 @@
         <v>0.74688657635395606</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -2715,7 +2732,7 @@
         <v>0.53794081650927705</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -2743,9 +2760,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -2757,9 +2774,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -2771,11 +2788,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2792,7 +2809,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2809,7 +2826,7 @@
         <v>-2.2843447109758301</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2826,7 +2843,7 @@
         <v>-8.4072251269262696E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2843,7 +2860,7 @@
         <v>0.29611171632314098</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2860,7 +2877,7 @@
         <v>1.75845186354745</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2877,7 +2894,7 @@
         <v>-0.76236366760055096</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2894,7 +2911,7 @@
         <v>0.62853290835895503</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -2911,7 +2928,7 @@
         <v>-8.7143718210927298E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -2928,7 +2945,7 @@
         <v>0.84698244904192099</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2945,7 +2962,7 @@
         <v>-0.73218305564943398</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -2962,7 +2979,7 @@
         <v>0.45176478094112998</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -2979,7 +2996,7 @@
         <v>-0.48116619434522001</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2996,7 +3013,7 @@
         <v>1.4416179829439899</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -3013,7 +3030,7 @@
         <v>-0.29043031142040199</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -3030,7 +3047,7 @@
         <v>0.41039596022329999</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -3047,7 +3064,7 @@
         <v>9.0586658239791298E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -3064,7 +3081,7 @@
         <v>-0.19878651280399501</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -3081,7 +3098,7 @@
         <v>-1.1921015273515501</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -3098,7 +3115,7 @@
         <v>1.5309831587774501</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -3115,7 +3132,7 @@
         <v>1.4171295501935499</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -3132,7 +3149,7 @@
         <v>1.50806209670647</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -3160,11 +3177,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3193,7 +3210,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -3222,7 +3239,7 @@
         <v>-1.6147478480366781</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -3251,7 +3268,7 @@
         <v>7.4319440477687015E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -3280,7 +3297,7 @@
         <v>0.34224551332283282</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -3309,7 +3326,7 @@
         <v>1.4386667878320649</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3338,7 +3355,7 @@
         <v>-0.86115985356668601</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3367,7 +3384,7 @@
         <v>0.54075932766897139</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -3396,7 +3413,7 @@
         <v>-0.16516560358472784</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3425,7 +3442,7 @@
         <v>0.69551525100246758</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -3454,7 +3471,7 @@
         <v>-0.99127220112166003</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3483,7 +3500,7 @@
         <v>0.53119309511533919</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -3512,7 +3529,7 @@
         <v>-0.35750972281162918</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -3541,7 +3558,7 @@
         <v>1.4839515989201006</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -3570,7 +3587,7 @@
         <v>-0.25606122082122978</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -3599,7 +3616,7 @@
         <v>0.57524958718309771</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -3628,7 +3645,7 @@
         <v>-0.20391093926790749</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -3657,7 +3674,7 @@
         <v>-0.2329747517241616</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -3686,7 +3703,7 @@
         <v>-1.1538461531171527</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -3715,7 +3732,7 @@
         <v>1.7090834292782853</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -3744,7 +3761,7 @@
         <v>1.2936133702251116</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -3773,7 +3790,7 @@
         <v>1.5494617093936773</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -3813,11 +3830,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3828,7 +3845,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -3839,7 +3856,7 @@
         <v>0.34657359027997264</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -3850,7 +3867,7 @@
         <v>0.23104906018664842</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -3861,7 +3878,7 @@
         <v>3.0136833937388925E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -3872,7 +3889,7 @@
         <v>2.7179999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3883,7 +3900,7 @@
         <v>2.5672117798516494E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3894,7 +3911,7 @@
         <v>1.7328679513998631E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -3905,7 +3922,7 @@
         <v>1.1002336199364211E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3916,7 +3933,7 @@
         <v>2.7179999999999999E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -3927,7 +3944,7 @@
         <v>2.7179999999999999E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3938,7 +3955,7 @@
         <v>7.453195489891885E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -3949,7 +3966,7 @@
         <v>7.7016353395549478E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -3960,7 +3977,7 @@
         <v>2.7179999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -3971,7 +3988,7 @@
         <v>6.9314718055994526E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -3982,7 +3999,7 @@
         <v>4.9510512897138946E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -3993,7 +4010,7 @@
         <v>1.6503504299046318E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -4004,7 +4021,7 @@
         <v>5.7762265046662105E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -4015,7 +4032,7 @@
         <v>1.332975347230664E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -4026,7 +4043,7 @@
         <v>1.2602676010180823E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -4037,7 +4054,7 @@
         <v>3.0136833937388925E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -4048,7 +4065,7 @@
         <v>3.0136833937388925E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -4070,11 +4087,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4085,7 +4102,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -4096,7 +4113,7 @@
         <v>0.22632780820666573</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -4107,7 +4124,7 @@
         <v>0.55521379565059015</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -4118,7 +4135,7 @@
         <v>0.17287454603478603</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -4129,7 +4146,7 @@
         <v>0.16999125421489655</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -4140,7 +4157,7 @@
         <v>0.19433009682781108</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -4151,7 +4168,7 @@
         <v>0.22428001203533895</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -4162,7 +4179,7 @@
         <v>5.4375125371813889E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -4173,7 +4190,7 @@
         <v>9.6231248933555655E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -4184,7 +4201,7 @@
         <v>0.3658670195100438</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -4195,7 +4212,7 @@
         <v>0.40082067594014675</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -4206,7 +4223,7 @@
         <v>0.11988807110995572</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -4217,7 +4234,7 @@
         <v>0.19553557227531512</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -4228,7 +4245,7 @@
         <v>0.42149594724160672</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -4239,7 +4256,7 @@
         <v>0.25140887760964525</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -4250,7 +4267,7 @@
         <v>0.4695684366567594</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -4261,7 +4278,7 @@
         <v>0.10912048970276542</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -4272,7 +4289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -4283,7 +4300,7 @@
         <v>0.74928855080194068</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -4294,7 +4311,7 @@
         <v>0.71642133761327131</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -4305,7 +4322,7 @@
         <v>1.1097370215502349</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -4327,11 +4344,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>46</v>
       </c>
@@ -4356,13 +4373,13 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B1" t="s">
         <v>3</v>
@@ -4410,7 +4427,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -4460,7 +4477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -4510,7 +4527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -4560,7 +4577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4610,7 +4627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -4660,7 +4677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -4710,7 +4727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -4760,7 +4777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -4810,7 +4827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -4860,7 +4877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -4910,7 +4927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -4960,7 +4977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -5010,7 +5027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -5060,7 +5077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -5110,7 +5127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -5160,7 +5177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="13" customHeight="1"/>
+    <row r="17" ht="13" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
